--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -1576,7 +1576,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129773546</v>
+        <v>129771712</v>
       </c>
       <c r="B11" t="n">
         <v>56926</v>
@@ -1609,20 +1609,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>429993</v>
+        <v>429958</v>
       </c>
       <c r="R11" t="n">
-        <v>6795617</v>
+        <v>6795551</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,19 +1669,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129771712</v>
+        <v>129773546</v>
       </c>
       <c r="B12" t="n">
         <v>56926</v>
@@ -1714,20 +1714,20 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>429958</v>
+        <v>429993</v>
       </c>
       <c r="R12" t="n">
-        <v>6795551</v>
+        <v>6795617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,12 +1774,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129771705</v>
       </c>
       <c r="B2" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129773550</v>
+        <v>129773547</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>91614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,31 +783,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430008</v>
+        <v>430042</v>
       </c>
       <c r="R3" t="n">
-        <v>6795618</v>
+        <v>6795556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129773547</v>
+        <v>129773550</v>
       </c>
       <c r="B4" t="n">
-        <v>91609</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,26 +884,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -915,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430042</v>
+        <v>430008</v>
       </c>
       <c r="R4" t="n">
-        <v>6795556</v>
+        <v>6795618</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +960,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129771756</v>
+        <v>129771709</v>
       </c>
       <c r="B5" t="n">
-        <v>78834</v>
+        <v>79176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430017</v>
+        <v>429972</v>
       </c>
       <c r="R5" t="n">
-        <v>6795360</v>
+        <v>6795453</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129771709</v>
+        <v>129771756</v>
       </c>
       <c r="B6" t="n">
-        <v>79171</v>
+        <v>78839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>429972</v>
+        <v>430017</v>
       </c>
       <c r="R6" t="n">
-        <v>6795453</v>
+        <v>6795360</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1175,7 @@
         <v>129773555</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>129771704</v>
       </c>
       <c r="B8" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,32 +1366,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129771735</v>
+        <v>129773545</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,20 +1399,20 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>429950</v>
+        <v>429964</v>
       </c>
       <c r="R9" t="n">
-        <v>6795610</v>
+        <v>6795609</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,44 +1459,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129773545</v>
+        <v>129771735</v>
       </c>
       <c r="B10" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,20 +1504,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>429964</v>
+        <v>429950</v>
       </c>
       <c r="R10" t="n">
-        <v>6795609</v>
+        <v>6795610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,12 +1564,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         <v>129773548</v>
       </c>
       <c r="B13" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>129773554</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>129771765</v>
       </c>
       <c r="B15" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>129773553</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129773551</v>
       </c>
       <c r="B19" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>129771780</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129771709</v>
+        <v>129771756</v>
       </c>
       <c r="B5" t="n">
-        <v>79176</v>
+        <v>78839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429972</v>
+        <v>430017</v>
       </c>
       <c r="R5" t="n">
-        <v>6795453</v>
+        <v>6795360</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129771756</v>
+        <v>129771709</v>
       </c>
       <c r="B6" t="n">
-        <v>78839</v>
+        <v>79176</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430017</v>
+        <v>429972</v>
       </c>
       <c r="R6" t="n">
-        <v>6795360</v>
+        <v>6795453</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129771765</v>
+        <v>129771734</v>
       </c>
       <c r="B15" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,34 +2000,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430018</v>
+        <v>429979</v>
       </c>
       <c r="R15" t="n">
-        <v>6795349</v>
+        <v>6795545</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,10 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129771734</v>
+        <v>129771765</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2097,42 +2105,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>429979</v>
+        <v>430018</v>
       </c>
       <c r="R16" t="n">
-        <v>6795545</v>
+        <v>6795349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129771756</v>
+        <v>129771709</v>
       </c>
       <c r="B5" t="n">
-        <v>78839</v>
+        <v>79176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430017</v>
+        <v>429972</v>
       </c>
       <c r="R5" t="n">
-        <v>6795360</v>
+        <v>6795453</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129771709</v>
+        <v>129771756</v>
       </c>
       <c r="B6" t="n">
-        <v>79176</v>
+        <v>78839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>429972</v>
+        <v>430017</v>
       </c>
       <c r="R6" t="n">
-        <v>6795453</v>
+        <v>6795360</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1366,32 +1366,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129773545</v>
+        <v>129771735</v>
       </c>
       <c r="B9" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,20 +1399,20 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>429964</v>
+        <v>429950</v>
       </c>
       <c r="R9" t="n">
-        <v>6795609</v>
+        <v>6795610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,44 +1459,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129771735</v>
+        <v>129773545</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,20 +1504,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>429950</v>
+        <v>429964</v>
       </c>
       <c r="R10" t="n">
-        <v>6795610</v>
+        <v>6795609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,19 +1564,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129771712</v>
+        <v>129773546</v>
       </c>
       <c r="B11" t="n">
         <v>56926</v>
@@ -1609,20 +1609,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>429958</v>
+        <v>429993</v>
       </c>
       <c r="R11" t="n">
-        <v>6795551</v>
+        <v>6795617</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,19 +1669,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129773546</v>
+        <v>129771712</v>
       </c>
       <c r="B12" t="n">
         <v>56926</v>
@@ -1714,20 +1714,20 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>429993</v>
+        <v>429958</v>
       </c>
       <c r="R12" t="n">
-        <v>6795617</v>
+        <v>6795551</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,12 +1774,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129771734</v>
+        <v>129771765</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,42 +2000,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>429979</v>
+        <v>430018</v>
       </c>
       <c r="R15" t="n">
-        <v>6795545</v>
+        <v>6795349</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,10 +2086,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129771765</v>
+        <v>129771734</v>
       </c>
       <c r="B16" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,34 +2097,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430018</v>
+        <v>429979</v>
       </c>
       <c r="R16" t="n">
-        <v>6795349</v>
+        <v>6795545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2490,45 +2490,61 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129771780</v>
+        <v>129771727</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>429986</v>
+        <v>429950</v>
       </c>
       <c r="R20" t="n">
-        <v>6795535</v>
+        <v>6795588</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2561,6 +2577,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2587,61 +2608,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129771727</v>
+        <v>129771780</v>
       </c>
       <c r="B21" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>429950</v>
+        <v>429986</v>
       </c>
       <c r="R21" t="n">
-        <v>6795588</v>
+        <v>6795535</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,11 +2679,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -1576,7 +1576,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129773546</v>
+        <v>129771712</v>
       </c>
       <c r="B11" t="n">
         <v>56926</v>
@@ -1609,20 +1609,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>429993</v>
+        <v>429958</v>
       </c>
       <c r="R11" t="n">
-        <v>6795617</v>
+        <v>6795551</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,19 +1669,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129771712</v>
+        <v>129773546</v>
       </c>
       <c r="B12" t="n">
         <v>56926</v>
@@ -1714,20 +1714,20 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>429958</v>
+        <v>429993</v>
       </c>
       <c r="R12" t="n">
-        <v>6795551</v>
+        <v>6795617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,12 +1774,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129771765</v>
+        <v>129771734</v>
       </c>
       <c r="B15" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,34 +2000,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430018</v>
+        <v>429979</v>
       </c>
       <c r="R15" t="n">
-        <v>6795349</v>
+        <v>6795545</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,10 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129771734</v>
+        <v>129771765</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2097,42 +2105,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>429979</v>
+        <v>430018</v>
       </c>
       <c r="R16" t="n">
-        <v>6795545</v>
+        <v>6795349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2490,61 +2490,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129771727</v>
+        <v>129771780</v>
       </c>
       <c r="B20" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>429950</v>
+        <v>429986</v>
       </c>
       <c r="R20" t="n">
-        <v>6795588</v>
+        <v>6795535</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,11 +2561,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,45 +2587,61 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129771780</v>
+        <v>129771727</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>429986</v>
+        <v>429950</v>
       </c>
       <c r="R21" t="n">
-        <v>6795535</v>
+        <v>6795588</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,6 +2674,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129773547</v>
+        <v>129773550</v>
       </c>
       <c r="B3" t="n">
-        <v>91614</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,26 +783,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -810,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430042</v>
+        <v>430008</v>
       </c>
       <c r="R3" t="n">
-        <v>6795556</v>
+        <v>6795618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +859,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129773550</v>
+        <v>129773547</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>91618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,31 +888,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430008</v>
+        <v>430042</v>
       </c>
       <c r="R4" t="n">
-        <v>6795618</v>
+        <v>6795556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +959,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129771709</v>
+        <v>129771756</v>
       </c>
       <c r="B5" t="n">
-        <v>79176</v>
+        <v>78839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429972</v>
+        <v>430017</v>
       </c>
       <c r="R5" t="n">
-        <v>6795453</v>
+        <v>6795360</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129771756</v>
+        <v>129771709</v>
       </c>
       <c r="B6" t="n">
-        <v>78839</v>
+        <v>79176</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430017</v>
+        <v>429972</v>
       </c>
       <c r="R6" t="n">
-        <v>6795360</v>
+        <v>6795453</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
         <v>129773548</v>
       </c>
       <c r="B13" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2490,45 +2490,61 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129771780</v>
+        <v>129771727</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>429986</v>
+        <v>429950</v>
       </c>
       <c r="R20" t="n">
-        <v>6795535</v>
+        <v>6795588</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2561,6 +2577,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2587,61 +2608,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129771727</v>
+        <v>129771780</v>
       </c>
       <c r="B21" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>429950</v>
+        <v>429986</v>
       </c>
       <c r="R21" t="n">
-        <v>6795588</v>
+        <v>6795535</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,11 +2679,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>129773547</v>
       </c>
       <c r="B4" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129771756</v>
+        <v>129771709</v>
       </c>
       <c r="B5" t="n">
-        <v>78839</v>
+        <v>79176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430017</v>
+        <v>429972</v>
       </c>
       <c r="R5" t="n">
-        <v>6795360</v>
+        <v>6795453</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129771709</v>
+        <v>129771756</v>
       </c>
       <c r="B6" t="n">
-        <v>79176</v>
+        <v>78839</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>429972</v>
+        <v>430017</v>
       </c>
       <c r="R6" t="n">
-        <v>6795453</v>
+        <v>6795360</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1366,32 +1366,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129771735</v>
+        <v>129773545</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,20 +1399,20 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>429950</v>
+        <v>429964</v>
       </c>
       <c r="R9" t="n">
-        <v>6795610</v>
+        <v>6795609</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,44 +1459,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129773545</v>
+        <v>129771735</v>
       </c>
       <c r="B10" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,20 +1504,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>429964</v>
+        <v>429950</v>
       </c>
       <c r="R10" t="n">
-        <v>6795609</v>
+        <v>6795610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,12 +1564,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         <v>129773548</v>
       </c>
       <c r="B13" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -1989,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129771734</v>
+        <v>129771765</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,42 +2000,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>429979</v>
+        <v>430018</v>
       </c>
       <c r="R15" t="n">
-        <v>6795545</v>
+        <v>6795349</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,10 +2086,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129771765</v>
+        <v>129771734</v>
       </c>
       <c r="B16" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,34 +2097,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430018</v>
+        <v>429979</v>
       </c>
       <c r="R16" t="n">
-        <v>6795349</v>
+        <v>6795545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129773550</v>
+        <v>129773547</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,31 +783,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430008</v>
+        <v>430042</v>
       </c>
       <c r="R3" t="n">
-        <v>6795618</v>
+        <v>6795556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129773547</v>
+        <v>129773550</v>
       </c>
       <c r="B4" t="n">
-        <v>91620</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,26 +884,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -915,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430042</v>
+        <v>430008</v>
       </c>
       <c r="R4" t="n">
-        <v>6795556</v>
+        <v>6795618</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +960,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129773547</v>
+        <v>129773550</v>
       </c>
       <c r="B3" t="n">
-        <v>91620</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,26 +783,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -810,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430042</v>
+        <v>430008</v>
       </c>
       <c r="R3" t="n">
-        <v>6795556</v>
+        <v>6795618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +859,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129773550</v>
+        <v>129773547</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>91620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,31 +888,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430008</v>
+        <v>430042</v>
       </c>
       <c r="R4" t="n">
-        <v>6795618</v>
+        <v>6795556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +959,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129771709</v>
+        <v>129771756</v>
       </c>
       <c r="B5" t="n">
-        <v>79176</v>
+        <v>78839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429972</v>
+        <v>430017</v>
       </c>
       <c r="R5" t="n">
-        <v>6795453</v>
+        <v>6795360</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129771756</v>
+        <v>129771709</v>
       </c>
       <c r="B6" t="n">
-        <v>78839</v>
+        <v>79176</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430017</v>
+        <v>429972</v>
       </c>
       <c r="R6" t="n">
-        <v>6795360</v>
+        <v>6795453</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1366,32 +1366,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129773545</v>
+        <v>129771735</v>
       </c>
       <c r="B9" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,20 +1399,20 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>429964</v>
+        <v>429950</v>
       </c>
       <c r="R9" t="n">
-        <v>6795609</v>
+        <v>6795610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,44 +1459,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129771735</v>
+        <v>129773545</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,20 +1504,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>429950</v>
+        <v>429964</v>
       </c>
       <c r="R10" t="n">
-        <v>6795610</v>
+        <v>6795609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,12 +1564,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2490,61 +2490,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129771727</v>
+        <v>129771780</v>
       </c>
       <c r="B20" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>429950</v>
+        <v>429986</v>
       </c>
       <c r="R20" t="n">
-        <v>6795588</v>
+        <v>6795535</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,11 +2561,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,45 +2587,61 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129771780</v>
+        <v>129771727</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>429986</v>
+        <v>429950</v>
       </c>
       <c r="R21" t="n">
-        <v>6795535</v>
+        <v>6795588</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,6 +2674,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129771705</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129773550</v>
+        <v>129773547</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>91623</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,31 +783,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430008</v>
+        <v>430042</v>
       </c>
       <c r="R3" t="n">
-        <v>6795618</v>
+        <v>6795556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129773547</v>
+        <v>129773550</v>
       </c>
       <c r="B4" t="n">
-        <v>91620</v>
+        <v>57734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,26 +884,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -915,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430042</v>
+        <v>430008</v>
       </c>
       <c r="R4" t="n">
-        <v>6795556</v>
+        <v>6795618</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +960,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,7 +981,7 @@
         <v>129771756</v>
       </c>
       <c r="B5" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129771709</v>
       </c>
       <c r="B6" t="n">
-        <v>79176</v>
+        <v>79179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>129773555</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>129771704</v>
       </c>
       <c r="B8" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,32 +1366,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129771735</v>
+        <v>129773545</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>56927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,20 +1399,20 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>429950</v>
+        <v>429964</v>
       </c>
       <c r="R9" t="n">
-        <v>6795610</v>
+        <v>6795609</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,44 +1459,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129773545</v>
+        <v>129771735</v>
       </c>
       <c r="B10" t="n">
-        <v>56926</v>
+        <v>57734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,20 +1504,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>429964</v>
+        <v>429950</v>
       </c>
       <c r="R10" t="n">
-        <v>6795609</v>
+        <v>6795610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,12 +1564,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1579,7 +1579,7 @@
         <v>129771712</v>
       </c>
       <c r="B11" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>129773546</v>
       </c>
       <c r="B12" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>129773548</v>
       </c>
       <c r="B13" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>129773554</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129771765</v>
+        <v>129771734</v>
       </c>
       <c r="B15" t="n">
-        <v>78838</v>
+        <v>57734</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,34 +2000,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>430018</v>
+        <v>429979</v>
       </c>
       <c r="R15" t="n">
-        <v>6795349</v>
+        <v>6795545</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,10 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129771734</v>
+        <v>129771765</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>78841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2097,42 +2105,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>429979</v>
+        <v>430018</v>
       </c>
       <c r="R16" t="n">
-        <v>6795545</v>
+        <v>6795349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,7 +2194,7 @@
         <v>129773549</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>129773553</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129773551</v>
       </c>
       <c r="B19" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>129771780</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>129771727</v>
       </c>
       <c r="B21" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129771756</v>
+        <v>129771709</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>79179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430017</v>
+        <v>429972</v>
       </c>
       <c r="R5" t="n">
-        <v>6795360</v>
+        <v>6795453</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129771709</v>
+        <v>129771756</v>
       </c>
       <c r="B6" t="n">
-        <v>79179</v>
+        <v>78842</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>429972</v>
+        <v>430017</v>
       </c>
       <c r="R6" t="n">
-        <v>6795453</v>
+        <v>6795360</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2490,45 +2490,61 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129771780</v>
+        <v>129771727</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>56927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>429986</v>
+        <v>429950</v>
       </c>
       <c r="R20" t="n">
-        <v>6795535</v>
+        <v>6795588</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2561,6 +2577,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2587,61 +2608,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129771727</v>
+        <v>129771780</v>
       </c>
       <c r="B21" t="n">
-        <v>56927</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>429950</v>
+        <v>429986</v>
       </c>
       <c r="R21" t="n">
-        <v>6795588</v>
+        <v>6795535</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,11 +2679,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129771705</v>
       </c>
       <c r="B2" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129773547</v>
       </c>
       <c r="B3" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129773550</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129771709</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129771756</v>
       </c>
       <c r="B6" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>129773555</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>129771704</v>
       </c>
       <c r="B8" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,32 +1366,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129773545</v>
+        <v>129771735</v>
       </c>
       <c r="B9" t="n">
-        <v>56927</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,20 +1399,20 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>429964</v>
+        <v>429950</v>
       </c>
       <c r="R9" t="n">
-        <v>6795609</v>
+        <v>6795610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,44 +1459,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129771735</v>
+        <v>129773545</v>
       </c>
       <c r="B10" t="n">
-        <v>57734</v>
+        <v>56930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,20 +1504,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>429950</v>
+        <v>429964</v>
       </c>
       <c r="R10" t="n">
-        <v>6795610</v>
+        <v>6795609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,12 +1564,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1579,7 +1579,7 @@
         <v>129771712</v>
       </c>
       <c r="B11" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>129773546</v>
       </c>
       <c r="B12" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>129773548</v>
       </c>
       <c r="B13" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>129773554</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>129771734</v>
       </c>
       <c r="B15" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>129771765</v>
       </c>
       <c r="B16" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129773549</v>
       </c>
       <c r="B17" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>129773553</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129773551</v>
       </c>
       <c r="B19" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>129771727</v>
       </c>
       <c r="B20" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>129771780</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -1366,32 +1366,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129771735</v>
+        <v>129773545</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>56930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,20 +1399,20 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>429950</v>
+        <v>429964</v>
       </c>
       <c r="R9" t="n">
-        <v>6795610</v>
+        <v>6795609</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,44 +1459,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129773545</v>
+        <v>129771735</v>
       </c>
       <c r="B10" t="n">
-        <v>56930</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,20 +1504,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>429964</v>
+        <v>429950</v>
       </c>
       <c r="R10" t="n">
-        <v>6795609</v>
+        <v>6795610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,12 +1564,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129773547</v>
+        <v>129773550</v>
       </c>
       <c r="B3" t="n">
-        <v>91626</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,26 +783,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -810,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430042</v>
+        <v>430008</v>
       </c>
       <c r="R3" t="n">
-        <v>6795556</v>
+        <v>6795618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +859,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129773550</v>
+        <v>129773547</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>91626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,31 +888,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430008</v>
+        <v>430042</v>
       </c>
       <c r="R4" t="n">
-        <v>6795618</v>
+        <v>6795556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +959,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1366,32 +1366,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129773545</v>
+        <v>129771735</v>
       </c>
       <c r="B9" t="n">
-        <v>56930</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,20 +1399,20 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>429964</v>
+        <v>429950</v>
       </c>
       <c r="R9" t="n">
-        <v>6795609</v>
+        <v>6795610</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,44 +1459,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129771735</v>
+        <v>129773545</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>56930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,20 +1504,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>429950</v>
+        <v>429964</v>
       </c>
       <c r="R10" t="n">
-        <v>6795610</v>
+        <v>6795609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,12 +1564,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129771705</v>
       </c>
       <c r="B2" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129773547</v>
       </c>
       <c r="B4" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129771709</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129771756</v>
       </c>
       <c r="B6" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>129773555</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>129771704</v>
       </c>
       <c r="B8" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>129773548</v>
       </c>
       <c r="B13" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>129773554</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129771734</v>
+        <v>129771765</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,42 +2000,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>429979</v>
+        <v>430018</v>
       </c>
       <c r="R15" t="n">
-        <v>6795545</v>
+        <v>6795349</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,10 +2086,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129771765</v>
+        <v>129771734</v>
       </c>
       <c r="B16" t="n">
-        <v>78844</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,34 +2097,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>430018</v>
+        <v>429979</v>
       </c>
       <c r="R16" t="n">
-        <v>6795349</v>
+        <v>6795545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2299,7 +2299,7 @@
         <v>129773553</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129773551</v>
       </c>
       <c r="B19" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2490,61 +2490,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129771727</v>
+        <v>129771780</v>
       </c>
       <c r="B20" t="n">
-        <v>56930</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>429950</v>
+        <v>429986</v>
       </c>
       <c r="R20" t="n">
-        <v>6795588</v>
+        <v>6795535</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,11 +2561,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,45 +2587,61 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129771780</v>
+        <v>129771727</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>56930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>429986</v>
+        <v>429950</v>
       </c>
       <c r="R21" t="n">
-        <v>6795535</v>
+        <v>6795588</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,6 +2674,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129773550</v>
+        <v>129773547</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>91627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,31 +783,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430008</v>
+        <v>430042</v>
       </c>
       <c r="R3" t="n">
-        <v>6795618</v>
+        <v>6795556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129773547</v>
+        <v>129773550</v>
       </c>
       <c r="B4" t="n">
-        <v>91627</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,26 +884,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -915,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430042</v>
+        <v>430008</v>
       </c>
       <c r="R4" t="n">
-        <v>6795556</v>
+        <v>6795618</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +960,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129771709</v>
+        <v>129771756</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429972</v>
+        <v>430017</v>
       </c>
       <c r="R5" t="n">
-        <v>6795453</v>
+        <v>6795360</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129771756</v>
+        <v>129771709</v>
       </c>
       <c r="B6" t="n">
-        <v>78846</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430017</v>
+        <v>429972</v>
       </c>
       <c r="R6" t="n">
-        <v>6795360</v>
+        <v>6795453</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129771712</v>
+        <v>129773546</v>
       </c>
       <c r="B11" t="n">
         <v>56930</v>
@@ -1609,20 +1609,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>429958</v>
+        <v>429993</v>
       </c>
       <c r="R11" t="n">
-        <v>6795551</v>
+        <v>6795617</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,19 +1669,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129773546</v>
+        <v>129771712</v>
       </c>
       <c r="B12" t="n">
         <v>56930</v>
@@ -1714,20 +1714,20 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>429993</v>
+        <v>429958</v>
       </c>
       <c r="R12" t="n">
-        <v>6795617</v>
+        <v>6795551</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,12 +1774,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2490,45 +2490,61 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129771780</v>
+        <v>129771727</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>429986</v>
+        <v>429950</v>
       </c>
       <c r="R20" t="n">
-        <v>6795535</v>
+        <v>6795588</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2561,6 +2577,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2587,61 +2608,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129771727</v>
+        <v>129771780</v>
       </c>
       <c r="B21" t="n">
-        <v>56930</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>429950</v>
+        <v>429986</v>
       </c>
       <c r="R21" t="n">
-        <v>6795588</v>
+        <v>6795535</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2674,11 +2679,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129773547</v>
+        <v>129773550</v>
       </c>
       <c r="B3" t="n">
-        <v>91627</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,26 +783,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -810,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430042</v>
+        <v>430008</v>
       </c>
       <c r="R3" t="n">
-        <v>6795556</v>
+        <v>6795618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +859,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129773550</v>
+        <v>129773547</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>91627</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,31 +888,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430008</v>
+        <v>430042</v>
       </c>
       <c r="R4" t="n">
-        <v>6795618</v>
+        <v>6795556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +959,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129773546</v>
+        <v>129771712</v>
       </c>
       <c r="B11" t="n">
         <v>56930</v>
@@ -1609,20 +1609,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>429993</v>
+        <v>429958</v>
       </c>
       <c r="R11" t="n">
-        <v>6795617</v>
+        <v>6795551</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,19 +1669,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129771712</v>
+        <v>129773546</v>
       </c>
       <c r="B12" t="n">
         <v>56930</v>
@@ -1714,20 +1714,20 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>429958</v>
+        <v>429993</v>
       </c>
       <c r="R12" t="n">
-        <v>6795551</v>
+        <v>6795617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,12 +1774,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129771705</v>
       </c>
       <c r="B2" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129773550</v>
+        <v>129773547</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>91644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,31 +783,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430008</v>
+        <v>430042</v>
       </c>
       <c r="R3" t="n">
-        <v>6795618</v>
+        <v>6795556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -877,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129773547</v>
+        <v>129773550</v>
       </c>
       <c r="B4" t="n">
-        <v>91627</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,26 +884,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -915,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430042</v>
+        <v>430008</v>
       </c>
       <c r="R4" t="n">
-        <v>6795556</v>
+        <v>6795618</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +960,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,7 +981,7 @@
         <v>129771756</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129771709</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79184</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>129773555</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>129771704</v>
       </c>
       <c r="B8" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,32 +1366,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129771735</v>
+        <v>129773545</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>56930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,20 +1399,20 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sötberg, Dlr</t>
+          <t>Stortjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>429950</v>
+        <v>429964</v>
       </c>
       <c r="R9" t="n">
-        <v>6795610</v>
+        <v>6795609</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,44 +1459,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129773545</v>
+        <v>129771735</v>
       </c>
       <c r="B10" t="n">
-        <v>56930</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,20 +1504,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stortjärnen, Dlr</t>
+          <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>429964</v>
+        <v>429950</v>
       </c>
       <c r="R10" t="n">
-        <v>6795609</v>
+        <v>6795610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,12 +1564,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         <v>129773548</v>
       </c>
       <c r="B13" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>129773554</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>129771765</v>
       </c>
       <c r="B15" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>129773553</v>
       </c>
       <c r="B18" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129773551</v>
       </c>
       <c r="B19" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2490,61 +2490,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129771727</v>
+        <v>129771780</v>
       </c>
       <c r="B20" t="n">
-        <v>56930</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>429950</v>
+        <v>429986</v>
       </c>
       <c r="R20" t="n">
-        <v>6795588</v>
+        <v>6795535</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2577,11 +2561,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,45 +2587,61 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129771780</v>
+        <v>129771727</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>56930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sötberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>429986</v>
+        <v>429950</v>
       </c>
       <c r="R21" t="n">
-        <v>6795535</v>
+        <v>6795588</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,6 +2674,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tuppar</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129771709</v>
+        <v>129771756</v>
       </c>
       <c r="B5" t="n">
-        <v>79190</v>
+        <v>78853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429972</v>
+        <v>430017</v>
       </c>
       <c r="R5" t="n">
-        <v>6795453</v>
+        <v>6795360</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129771756</v>
+        <v>129771709</v>
       </c>
       <c r="B6" t="n">
-        <v>78853</v>
+        <v>79190</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430017</v>
+        <v>429972</v>
       </c>
       <c r="R6" t="n">
-        <v>6795360</v>
+        <v>6795453</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 50070-2025 artfynd.xlsx
+++ b/artfynd/A 50070-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129771709</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129773547</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129773548</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129771780</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129773553</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129773554</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,6 +1399,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129773555</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129771765</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1558,6 +1603,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129773551</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1655,6 +1705,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129771704</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1752,6 +1807,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129771705</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1857,6 +1917,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129771734</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1962,6 +2027,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129771735</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2067,6 +2137,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129773549</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129773550</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2277,6 +2357,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129771712</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2395,6 +2480,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129771727</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2500,6 +2590,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129773545</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2605,6 +2700,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129773546</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2702,8 +2802,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129771756</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>